--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20241120120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2024-11-20T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -567,6 +567,12 @@
   </si>
   <si>
     <t>Conseiller en génétique</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Coordonnateur de parcours</t>
   </si>
   <si>
     <t>331</t>
@@ -1317,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1630,18 +1636,26 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>114</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>114</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="B40" t="s" s="2">
-        <v>198</v>
+      <c r="B41" t="s" s="2">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
